--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>235</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>65</v>
+        <v>343</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>211</v>
       </c>
       <c r="D3">
-        <v>306</v>
+        <v>165</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="D3">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>426</v>
